--- a/Excel025-div-rank.xlsx
+++ b/Excel025-div-rank.xlsx
@@ -501,10 +501,10 @@
         <v>534750</v>
       </c>
       <c r="E2" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="F2" t="n">
-        <v>465750</v>
+        <v>448500</v>
       </c>
       <c r="G2" t="n">
         <v>3</v>
@@ -513,7 +513,7 @@
         <v>10.1</v>
       </c>
       <c r="I2" t="n">
-        <v>11.59</v>
+        <v>12.04</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -575,10 +575,10 @@
         <v>1148400</v>
       </c>
       <c r="E4" t="n">
-        <v>8.35</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>626250</v>
+        <v>641250</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -587,7 +587,7 @@
         <v>4.9</v>
       </c>
       <c r="I4" t="n">
-        <v>8.98</v>
+        <v>8.77</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
@@ -599,223 +599,223 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NER</t>
+          <t>AIMIRT</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27000</v>
+        <v>17500</v>
       </c>
       <c r="C5" t="n">
-        <v>7.45</v>
+        <v>10.6</v>
       </c>
       <c r="D5" t="n">
-        <v>201150</v>
+        <v>185500</v>
       </c>
       <c r="E5" t="n">
-        <v>4.48</v>
+        <v>10.9</v>
       </c>
       <c r="F5" t="n">
-        <v>120960</v>
+        <v>190750</v>
       </c>
       <c r="G5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H5" t="n">
-        <v>4.83</v>
+        <v>7.92</v>
       </c>
       <c r="I5" t="n">
-        <v>8.039999999999999</v>
+        <v>7.71</v>
       </c>
       <c r="J5" t="n">
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>9720</v>
+        <v>14700</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AIMIRT</t>
+          <t>NER</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17500</v>
+        <v>27000</v>
       </c>
       <c r="C6" t="n">
-        <v>10.6</v>
+        <v>7.45</v>
       </c>
       <c r="D6" t="n">
-        <v>185500</v>
+        <v>201150</v>
       </c>
       <c r="E6" t="n">
-        <v>10.9</v>
+        <v>4.78</v>
       </c>
       <c r="F6" t="n">
-        <v>190750</v>
+        <v>129060</v>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H6" t="n">
-        <v>7.92</v>
+        <v>4.83</v>
       </c>
       <c r="I6" t="n">
-        <v>7.71</v>
+        <v>7.53</v>
       </c>
       <c r="J6" t="n">
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>14700</v>
+        <v>9720</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TFFIF</t>
+          <t>WHAIR</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="C7" t="n">
-        <v>7.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>144000</v>
+        <v>435000</v>
       </c>
       <c r="E7" t="n">
         <v>6.25</v>
       </c>
       <c r="F7" t="n">
-        <v>125000</v>
+        <v>312500</v>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>6.43</v>
+        <v>5.24</v>
       </c>
       <c r="I7" t="n">
-        <v>7.41</v>
+        <v>7.29</v>
       </c>
       <c r="J7" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>9266</v>
+        <v>22785</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WHAIR</t>
+          <t>TFFIF</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50000</v>
+        <v>20000</v>
       </c>
       <c r="C8" t="n">
-        <v>8.699999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="D8" t="n">
-        <v>435000</v>
+        <v>144000</v>
       </c>
       <c r="E8" t="n">
-        <v>6.15</v>
+        <v>6.6</v>
       </c>
       <c r="F8" t="n">
-        <v>307500</v>
+        <v>132000</v>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H8" t="n">
-        <v>5.24</v>
+        <v>6.43</v>
       </c>
       <c r="I8" t="n">
-        <v>7.41</v>
+        <v>7.02</v>
       </c>
       <c r="J8" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="K8" t="n">
-        <v>22785</v>
+        <v>9266</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PTT</t>
+          <t>SENA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7500</v>
+        <v>105000</v>
       </c>
       <c r="C9" t="n">
-        <v>32</v>
+        <v>4.48</v>
       </c>
       <c r="D9" t="n">
-        <v>240000</v>
+        <v>470400</v>
       </c>
       <c r="E9" t="n">
-        <v>32</v>
+        <v>1.69</v>
       </c>
       <c r="F9" t="n">
-        <v>240000</v>
+        <v>177450</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H9" t="n">
-        <v>6.88</v>
+        <v>2.48</v>
       </c>
       <c r="I9" t="n">
-        <v>6.88</v>
+        <v>6.58</v>
       </c>
       <c r="J9" t="n">
         <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>16500</v>
+        <v>11676</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SENA</t>
+          <t>PTT</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>105000</v>
+        <v>7500</v>
       </c>
       <c r="C10" t="n">
-        <v>4.48</v>
+        <v>32</v>
       </c>
       <c r="D10" t="n">
-        <v>470400</v>
+        <v>240000</v>
       </c>
       <c r="E10" t="n">
-        <v>1.69</v>
+        <v>34</v>
       </c>
       <c r="F10" t="n">
-        <v>177450</v>
+        <v>255000</v>
       </c>
       <c r="G10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>2.48</v>
+        <v>6.88</v>
       </c>
       <c r="I10" t="n">
-        <v>6.58</v>
+        <v>6.47</v>
       </c>
       <c r="J10" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="K10" t="n">
-        <v>11676</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="11">
@@ -849,7 +849,7 @@
         <v>6.47</v>
       </c>
       <c r="J11" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="K11" t="n">
         <v>13840</v>

--- a/Excel025-div-rank.xlsx
+++ b/Excel025-div-rank.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,395 +501,432 @@
         <v>534750</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5</v>
+        <v>6.65</v>
       </c>
       <c r="F2" t="n">
-        <v>448500</v>
+        <v>458850</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>10.1</v>
+        <v>10.04</v>
       </c>
       <c r="I2" t="n">
-        <v>12.04</v>
+        <v>11.7</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>53985.6</v>
+        <v>53695.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DIF</t>
+          <t>MCS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45000</v>
+        <v>75000</v>
       </c>
       <c r="C3" t="n">
-        <v>12.7</v>
+        <v>15.312</v>
       </c>
       <c r="D3" t="n">
-        <v>571500</v>
+        <v>1148400</v>
       </c>
       <c r="E3" t="n">
-        <v>9.449999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="F3" t="n">
-        <v>425250</v>
+        <v>712500</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="I3" t="n">
-        <v>9.41</v>
+        <v>10</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>39996</v>
+        <v>71250</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MCS</t>
+          <t>DIF</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>75000</v>
+        <v>45000</v>
       </c>
       <c r="C4" t="n">
-        <v>15.312</v>
+        <v>12.7</v>
       </c>
       <c r="D4" t="n">
-        <v>1148400</v>
+        <v>571500</v>
       </c>
       <c r="E4" t="n">
-        <v>8.550000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="F4" t="n">
-        <v>641250</v>
+        <v>432000</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="I4" t="n">
-        <v>8.77</v>
+        <v>9.26</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>56250</v>
+        <v>39996</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AIMIRT</t>
+          <t>WHAIR</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17500</v>
+        <v>50000</v>
       </c>
       <c r="C5" t="n">
-        <v>10.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>185500</v>
+        <v>435000</v>
       </c>
       <c r="E5" t="n">
-        <v>10.9</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>190750</v>
+        <v>350000</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>7.92</v>
+        <v>6.59</v>
       </c>
       <c r="I5" t="n">
-        <v>7.71</v>
+        <v>8.19</v>
       </c>
       <c r="J5" t="n">
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>14700</v>
+        <v>28650</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NER</t>
+          <t>3BBIF</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27000</v>
+        <v>120000</v>
       </c>
       <c r="C6" t="n">
-        <v>7.45</v>
+        <v>10.1</v>
       </c>
       <c r="D6" t="n">
-        <v>201150</v>
+        <v>1212000</v>
       </c>
       <c r="E6" t="n">
-        <v>4.78</v>
+        <v>6.7</v>
       </c>
       <c r="F6" t="n">
-        <v>129060</v>
+        <v>804000</v>
       </c>
       <c r="G6" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>4.83</v>
+        <v>5.11</v>
       </c>
       <c r="I6" t="n">
-        <v>7.53</v>
+        <v>7.7</v>
       </c>
       <c r="J6" t="n">
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>9720</v>
+        <v>61908</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WHAIR</t>
+          <t>AIMIRT</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>50000</v>
+        <v>17500</v>
       </c>
       <c r="C7" t="n">
-        <v>8.699999999999999</v>
+        <v>10.6</v>
       </c>
       <c r="D7" t="n">
-        <v>435000</v>
+        <v>185500</v>
       </c>
       <c r="E7" t="n">
-        <v>6.25</v>
+        <v>11.4</v>
       </c>
       <c r="F7" t="n">
-        <v>312500</v>
+        <v>199500</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>9.5</v>
       </c>
       <c r="H7" t="n">
-        <v>5.24</v>
+        <v>7.83</v>
       </c>
       <c r="I7" t="n">
-        <v>7.29</v>
+        <v>7.28</v>
       </c>
       <c r="J7" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="K7" t="n">
-        <v>22785</v>
+        <v>14525</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TFFIF</t>
+          <t>SENA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20000</v>
+        <v>105000</v>
       </c>
       <c r="C8" t="n">
-        <v>7.2</v>
+        <v>4.48</v>
       </c>
       <c r="D8" t="n">
-        <v>144000</v>
+        <v>470400</v>
       </c>
       <c r="E8" t="n">
-        <v>6.6</v>
+        <v>1.9</v>
       </c>
       <c r="F8" t="n">
-        <v>132000</v>
+        <v>199500</v>
       </c>
       <c r="G8" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="H8" t="n">
-        <v>6.43</v>
+        <v>3.09</v>
       </c>
       <c r="I8" t="n">
-        <v>7.02</v>
+        <v>7.28</v>
       </c>
       <c r="J8" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="K8" t="n">
-        <v>9266</v>
+        <v>14521.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SENA</t>
+          <t>TFFIF</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>105000</v>
+        <v>20000</v>
       </c>
       <c r="C9" t="n">
-        <v>4.48</v>
+        <v>7.2</v>
       </c>
       <c r="D9" t="n">
-        <v>470400</v>
+        <v>144000</v>
       </c>
       <c r="E9" t="n">
-        <v>1.69</v>
+        <v>6.8</v>
       </c>
       <c r="F9" t="n">
-        <v>177450</v>
+        <v>136000</v>
       </c>
       <c r="G9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H9" t="n">
-        <v>2.48</v>
+        <v>6.48</v>
       </c>
       <c r="I9" t="n">
-        <v>6.58</v>
+        <v>6.86</v>
       </c>
       <c r="J9" t="n">
         <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>11676</v>
+        <v>9326</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PTT</t>
+          <t>CPNREIT</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7500</v>
+        <v>55000</v>
       </c>
       <c r="C10" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D10" t="n">
-        <v>240000</v>
+        <v>990000</v>
       </c>
       <c r="E10" t="n">
-        <v>34</v>
+        <v>12.1</v>
       </c>
       <c r="F10" t="n">
-        <v>255000</v>
+        <v>665500</v>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>6.88</v>
+        <v>4.58</v>
       </c>
       <c r="I10" t="n">
-        <v>6.47</v>
+        <v>6.82</v>
       </c>
       <c r="J10" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>16500</v>
+        <v>45380.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WHART</t>
+          <t>NER</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20000</v>
+        <v>27000</v>
       </c>
       <c r="C11" t="n">
-        <v>12.3</v>
+        <v>7.45</v>
       </c>
       <c r="D11" t="n">
-        <v>246000</v>
+        <v>201150</v>
       </c>
       <c r="E11" t="n">
-        <v>10.7</v>
+        <v>4.92</v>
       </c>
       <c r="F11" t="n">
-        <v>214000</v>
+        <v>132840</v>
       </c>
       <c r="G11" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H11" t="n">
-        <v>5.63</v>
+        <v>4.16</v>
       </c>
       <c r="I11" t="n">
-        <v>6.47</v>
+        <v>6.3</v>
       </c>
       <c r="J11" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="K11" t="n">
-        <v>13840</v>
+        <v>8370</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CPNREIT</t>
+          <t>PTT</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>55000</v>
+        <v>7500</v>
       </c>
       <c r="C12" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D12" t="n">
-        <v>990000</v>
+        <v>240000</v>
       </c>
       <c r="E12" t="n">
-        <v>11.3</v>
+        <v>37</v>
       </c>
       <c r="F12" t="n">
-        <v>621500</v>
+        <v>277500</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H12" t="n">
-        <v>3.58</v>
+        <v>7.19</v>
       </c>
       <c r="I12" t="n">
-        <v>5.7</v>
+        <v>6.22</v>
       </c>
       <c r="J12" t="n">
         <v>11</v>
       </c>
       <c r="K12" t="n">
-        <v>35442</v>
+        <v>17250</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>WHART</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C13" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>246000</v>
+      </c>
+      <c r="E13" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>224000</v>
+      </c>
+      <c r="G13" t="n">
+        <v>8</v>
+      </c>
+      <c r="H13" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="I13" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="J13" t="n">
+        <v>12</v>
+      </c>
+      <c r="K13" t="n">
+        <v>13548</v>
       </c>
     </row>
   </sheetData>

--- a/Excel025-div-rank.xlsx
+++ b/Excel025-div-rank.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,10 +501,10 @@
         <v>534750</v>
       </c>
       <c r="E2" t="n">
-        <v>6.65</v>
+        <v>6.4</v>
       </c>
       <c r="F2" t="n">
-        <v>458850</v>
+        <v>441600</v>
       </c>
       <c r="G2" t="n">
         <v>4</v>
@@ -513,7 +513,7 @@
         <v>10.04</v>
       </c>
       <c r="I2" t="n">
-        <v>11.7</v>
+        <v>12.16</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -538,10 +538,10 @@
         <v>1148400</v>
       </c>
       <c r="E3" t="n">
-        <v>9.5</v>
+        <v>9.25</v>
       </c>
       <c r="F3" t="n">
-        <v>712500</v>
+        <v>693750</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
@@ -550,7 +550,7 @@
         <v>6.2</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>10.27</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
@@ -575,10 +575,10 @@
         <v>571500</v>
       </c>
       <c r="E4" t="n">
-        <v>9.6</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>432000</v>
+        <v>425250</v>
       </c>
       <c r="G4" t="n">
         <v>5</v>
@@ -587,7 +587,7 @@
         <v>7</v>
       </c>
       <c r="I4" t="n">
-        <v>9.26</v>
+        <v>9.41</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
@@ -612,10 +612,10 @@
         <v>435000</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="F5" t="n">
-        <v>350000</v>
+        <v>335000</v>
       </c>
       <c r="G5" t="n">
         <v>6</v>
@@ -624,7 +624,7 @@
         <v>6.59</v>
       </c>
       <c r="I5" t="n">
-        <v>8.19</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="J5" t="n">
         <v>4</v>
@@ -649,10 +649,10 @@
         <v>1212000</v>
       </c>
       <c r="E6" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="F6" t="n">
-        <v>804000</v>
+        <v>780000</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -661,7 +661,7 @@
         <v>5.11</v>
       </c>
       <c r="I6" t="n">
-        <v>7.7</v>
+        <v>7.94</v>
       </c>
       <c r="J6" t="n">
         <v>5</v>
@@ -673,260 +673,223 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AIMIRT</t>
+          <t>SENA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17500</v>
+        <v>105000</v>
       </c>
       <c r="C7" t="n">
-        <v>10.6</v>
+        <v>4.48</v>
       </c>
       <c r="D7" t="n">
-        <v>185500</v>
+        <v>470400</v>
       </c>
       <c r="E7" t="n">
-        <v>11.4</v>
+        <v>1.84</v>
       </c>
       <c r="F7" t="n">
-        <v>199500</v>
+        <v>193200</v>
       </c>
       <c r="G7" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="H7" t="n">
-        <v>7.83</v>
+        <v>3.09</v>
       </c>
       <c r="I7" t="n">
-        <v>7.28</v>
+        <v>7.52</v>
       </c>
       <c r="J7" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>14525</v>
+        <v>14521.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SENA</t>
+          <t>TFFIF</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>105000</v>
+        <v>25000</v>
       </c>
       <c r="C8" t="n">
-        <v>4.48</v>
+        <v>7.3</v>
       </c>
       <c r="D8" t="n">
-        <v>470400</v>
+        <v>182500</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9</v>
+        <v>6.5</v>
       </c>
       <c r="F8" t="n">
-        <v>199500</v>
+        <v>162500</v>
       </c>
       <c r="G8" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="H8" t="n">
-        <v>3.09</v>
+        <v>6.39</v>
       </c>
       <c r="I8" t="n">
-        <v>7.28</v>
+        <v>7.17</v>
       </c>
       <c r="J8" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="K8" t="n">
-        <v>14521.5</v>
+        <v>11657.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TFFIF</t>
+          <t>CPNREIT</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20000</v>
+        <v>55000</v>
       </c>
       <c r="C9" t="n">
-        <v>7.2</v>
+        <v>18</v>
       </c>
       <c r="D9" t="n">
-        <v>144000</v>
+        <v>990000</v>
       </c>
       <c r="E9" t="n">
-        <v>6.8</v>
+        <v>11.7</v>
       </c>
       <c r="F9" t="n">
-        <v>136000</v>
+        <v>643500</v>
       </c>
       <c r="G9" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>6.48</v>
+        <v>4.58</v>
       </c>
       <c r="I9" t="n">
-        <v>6.86</v>
+        <v>7.05</v>
       </c>
       <c r="J9" t="n">
         <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>9326</v>
+        <v>45380.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CPNREIT</t>
+          <t>PTT</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>55000</v>
+        <v>7500</v>
       </c>
       <c r="C10" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D10" t="n">
-        <v>990000</v>
+        <v>240000</v>
       </c>
       <c r="E10" t="n">
-        <v>12.1</v>
+        <v>34</v>
       </c>
       <c r="F10" t="n">
-        <v>665500</v>
+        <v>255000</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>4.58</v>
+        <v>7.19</v>
       </c>
       <c r="I10" t="n">
-        <v>6.82</v>
+        <v>6.76</v>
       </c>
       <c r="J10" t="n">
         <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>45380.5</v>
+        <v>17250</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NER</t>
+          <t>WHART</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27000</v>
+        <v>20000</v>
       </c>
       <c r="C11" t="n">
-        <v>7.45</v>
+        <v>12.3</v>
       </c>
       <c r="D11" t="n">
-        <v>201150</v>
+        <v>246000</v>
       </c>
       <c r="E11" t="n">
-        <v>4.92</v>
+        <v>10.2</v>
       </c>
       <c r="F11" t="n">
-        <v>132840</v>
+        <v>204000</v>
       </c>
       <c r="G11" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H11" t="n">
-        <v>4.16</v>
+        <v>5.51</v>
       </c>
       <c r="I11" t="n">
-        <v>6.3</v>
+        <v>6.64</v>
       </c>
       <c r="J11" t="n">
         <v>10</v>
       </c>
       <c r="K11" t="n">
-        <v>8370</v>
+        <v>13548</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PTT</t>
+          <t>NER</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7500</v>
+        <v>27000</v>
       </c>
       <c r="C12" t="n">
-        <v>32</v>
+        <v>7.45</v>
       </c>
       <c r="D12" t="n">
-        <v>240000</v>
+        <v>201150</v>
       </c>
       <c r="E12" t="n">
-        <v>37</v>
+        <v>4.76</v>
       </c>
       <c r="F12" t="n">
-        <v>277500</v>
+        <v>128520</v>
       </c>
       <c r="G12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>7.19</v>
+        <v>4.16</v>
       </c>
       <c r="I12" t="n">
-        <v>6.22</v>
+        <v>6.51</v>
       </c>
       <c r="J12" t="n">
         <v>11</v>
       </c>
       <c r="K12" t="n">
-        <v>17250</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>WHART</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>20000</v>
-      </c>
-      <c r="C13" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="D13" t="n">
-        <v>246000</v>
-      </c>
-      <c r="E13" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="F13" t="n">
-        <v>224000</v>
-      </c>
-      <c r="G13" t="n">
-        <v>8</v>
-      </c>
-      <c r="H13" t="n">
-        <v>5.51</v>
-      </c>
-      <c r="I13" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="J13" t="n">
-        <v>12</v>
-      </c>
-      <c r="K13" t="n">
-        <v>13548</v>
+        <v>8370</v>
       </c>
     </row>
   </sheetData>

--- a/Excel025-div-rank.xlsx
+++ b/Excel025-div-rank.xlsx
@@ -538,10 +538,10 @@
         <v>1148400</v>
       </c>
       <c r="E3" t="n">
-        <v>9.25</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>693750</v>
+        <v>708750</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
@@ -550,7 +550,7 @@
         <v>6.2</v>
       </c>
       <c r="I3" t="n">
-        <v>10.27</v>
+        <v>10.05</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
@@ -612,10 +612,10 @@
         <v>435000</v>
       </c>
       <c r="E5" t="n">
-        <v>6.7</v>
+        <v>6.95</v>
       </c>
       <c r="F5" t="n">
-        <v>335000</v>
+        <v>347500</v>
       </c>
       <c r="G5" t="n">
         <v>6</v>
@@ -624,7 +624,7 @@
         <v>6.59</v>
       </c>
       <c r="I5" t="n">
-        <v>8.550000000000001</v>
+        <v>8.24</v>
       </c>
       <c r="J5" t="n">
         <v>4</v>
@@ -649,10 +649,10 @@
         <v>1212000</v>
       </c>
       <c r="E6" t="n">
-        <v>6.5</v>
+        <v>6.55</v>
       </c>
       <c r="F6" t="n">
-        <v>780000</v>
+        <v>786000</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -661,7 +661,7 @@
         <v>5.11</v>
       </c>
       <c r="I6" t="n">
-        <v>7.94</v>
+        <v>7.88</v>
       </c>
       <c r="J6" t="n">
         <v>5</v>
@@ -686,10 +686,10 @@
         <v>470400</v>
       </c>
       <c r="E7" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="F7" t="n">
-        <v>193200</v>
+        <v>195300</v>
       </c>
       <c r="G7" t="n">
         <v>9</v>
@@ -698,7 +698,7 @@
         <v>3.09</v>
       </c>
       <c r="I7" t="n">
-        <v>7.52</v>
+        <v>7.44</v>
       </c>
       <c r="J7" t="n">
         <v>6</v>
@@ -723,10 +723,10 @@
         <v>182500</v>
       </c>
       <c r="E8" t="n">
-        <v>6.5</v>
+        <v>6.55</v>
       </c>
       <c r="F8" t="n">
-        <v>162500</v>
+        <v>163750</v>
       </c>
       <c r="G8" t="n">
         <v>10</v>
@@ -735,7 +735,7 @@
         <v>6.39</v>
       </c>
       <c r="I8" t="n">
-        <v>7.17</v>
+        <v>7.12</v>
       </c>
       <c r="J8" t="n">
         <v>7</v>
@@ -760,10 +760,10 @@
         <v>990000</v>
       </c>
       <c r="E9" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="F9" t="n">
-        <v>643500</v>
+        <v>638000</v>
       </c>
       <c r="G9" t="n">
         <v>3</v>
@@ -772,7 +772,7 @@
         <v>4.58</v>
       </c>
       <c r="I9" t="n">
-        <v>7.05</v>
+        <v>7.11</v>
       </c>
       <c r="J9" t="n">
         <v>8</v>
@@ -797,10 +797,10 @@
         <v>240000</v>
       </c>
       <c r="E10" t="n">
-        <v>34</v>
+        <v>34.5</v>
       </c>
       <c r="F10" t="n">
-        <v>255000</v>
+        <v>258750</v>
       </c>
       <c r="G10" t="n">
         <v>7</v>
@@ -809,7 +809,7 @@
         <v>7.19</v>
       </c>
       <c r="I10" t="n">
-        <v>6.76</v>
+        <v>6.67</v>
       </c>
       <c r="J10" t="n">
         <v>9</v>
@@ -871,10 +871,10 @@
         <v>201150</v>
       </c>
       <c r="E12" t="n">
-        <v>4.76</v>
+        <v>4.88</v>
       </c>
       <c r="F12" t="n">
-        <v>128520</v>
+        <v>131760</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
@@ -883,7 +883,7 @@
         <v>4.16</v>
       </c>
       <c r="I12" t="n">
-        <v>6.51</v>
+        <v>6.35</v>
       </c>
       <c r="J12" t="n">
         <v>11</v>

--- a/Excel025-div-rank.xlsx
+++ b/Excel025-div-rank.xlsx
@@ -488,75 +488,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GVREIT</t>
+          <t>MCS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>69000</v>
+        <v>80000</v>
       </c>
       <c r="C2" t="n">
-        <v>7.75</v>
+        <v>14.85</v>
       </c>
       <c r="D2" t="n">
-        <v>534750</v>
+        <v>1188000</v>
       </c>
       <c r="E2" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>648000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" t="n">
         <v>6.4</v>
       </c>
-      <c r="F2" t="n">
-        <v>441600</v>
-      </c>
-      <c r="G2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H2" t="n">
-        <v>10.04</v>
-      </c>
       <c r="I2" t="n">
-        <v>12.16</v>
+        <v>11.73</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>53695.8</v>
+        <v>76000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MCS</t>
+          <t>GVREIT</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>75000</v>
+        <v>69000</v>
       </c>
       <c r="C3" t="n">
-        <v>15.312</v>
+        <v>7.75</v>
       </c>
       <c r="D3" t="n">
-        <v>1148400</v>
+        <v>534750</v>
       </c>
       <c r="E3" t="n">
-        <v>9.449999999999999</v>
+        <v>6.75</v>
       </c>
       <c r="F3" t="n">
-        <v>708750</v>
+        <v>465750</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>6.2</v>
+        <v>10.04</v>
       </c>
       <c r="I3" t="n">
-        <v>10.05</v>
+        <v>11.53</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>71250</v>
+        <v>53695.8</v>
       </c>
     </row>
     <row r="4">
@@ -575,10 +575,10 @@
         <v>571500</v>
       </c>
       <c r="E4" t="n">
-        <v>9.449999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="F4" t="n">
-        <v>425250</v>
+        <v>454500</v>
       </c>
       <c r="G4" t="n">
         <v>5</v>
@@ -587,7 +587,7 @@
         <v>7</v>
       </c>
       <c r="I4" t="n">
-        <v>9.41</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
@@ -612,10 +612,10 @@
         <v>435000</v>
       </c>
       <c r="E5" t="n">
-        <v>6.95</v>
+        <v>7.6</v>
       </c>
       <c r="F5" t="n">
-        <v>347500</v>
+        <v>380000</v>
       </c>
       <c r="G5" t="n">
         <v>6</v>
@@ -624,7 +624,7 @@
         <v>6.59</v>
       </c>
       <c r="I5" t="n">
-        <v>8.24</v>
+        <v>7.54</v>
       </c>
       <c r="J5" t="n">
         <v>4</v>
@@ -649,10 +649,10 @@
         <v>1212000</v>
       </c>
       <c r="E6" t="n">
-        <v>6.55</v>
+        <v>6.9</v>
       </c>
       <c r="F6" t="n">
-        <v>786000</v>
+        <v>828000</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -661,7 +661,7 @@
         <v>5.11</v>
       </c>
       <c r="I6" t="n">
-        <v>7.88</v>
+        <v>7.48</v>
       </c>
       <c r="J6" t="n">
         <v>5</v>
@@ -686,10 +686,10 @@
         <v>470400</v>
       </c>
       <c r="E7" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="F7" t="n">
-        <v>195300</v>
+        <v>202650</v>
       </c>
       <c r="G7" t="n">
         <v>9</v>
@@ -698,7 +698,7 @@
         <v>3.09</v>
       </c>
       <c r="I7" t="n">
-        <v>7.44</v>
+        <v>7.17</v>
       </c>
       <c r="J7" t="n">
         <v>6</v>
@@ -760,19 +760,19 @@
         <v>990000</v>
       </c>
       <c r="E9" t="n">
-        <v>11.6</v>
+        <v>12.2</v>
       </c>
       <c r="F9" t="n">
-        <v>638000</v>
+        <v>671000</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>4.58</v>
       </c>
       <c r="I9" t="n">
-        <v>7.11</v>
+        <v>6.76</v>
       </c>
       <c r="J9" t="n">
         <v>8</v>
@@ -784,112 +784,112 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PTT</t>
+          <t>NER</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7500</v>
+        <v>27000</v>
       </c>
       <c r="C10" t="n">
-        <v>32</v>
+        <v>7.45</v>
       </c>
       <c r="D10" t="n">
-        <v>240000</v>
+        <v>201150</v>
       </c>
       <c r="E10" t="n">
-        <v>34.5</v>
+        <v>4.68</v>
       </c>
       <c r="F10" t="n">
-        <v>258750</v>
+        <v>126360</v>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H10" t="n">
-        <v>7.19</v>
+        <v>4.16</v>
       </c>
       <c r="I10" t="n">
-        <v>6.67</v>
+        <v>6.62</v>
       </c>
       <c r="J10" t="n">
         <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>17250</v>
+        <v>8370</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WHART</t>
+          <t>PTT</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20000</v>
+        <v>7500</v>
       </c>
       <c r="C11" t="n">
-        <v>12.3</v>
+        <v>32</v>
       </c>
       <c r="D11" t="n">
-        <v>246000</v>
+        <v>240000</v>
       </c>
       <c r="E11" t="n">
-        <v>10.2</v>
+        <v>35.25</v>
       </c>
       <c r="F11" t="n">
-        <v>204000</v>
+        <v>264375</v>
       </c>
       <c r="G11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H11" t="n">
-        <v>5.51</v>
+        <v>7.19</v>
       </c>
       <c r="I11" t="n">
-        <v>6.64</v>
+        <v>6.52</v>
       </c>
       <c r="J11" t="n">
         <v>10</v>
       </c>
       <c r="K11" t="n">
-        <v>13548</v>
+        <v>17250</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NER</t>
+          <t>WHART</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>27000</v>
+        <v>20000</v>
       </c>
       <c r="C12" t="n">
-        <v>7.45</v>
+        <v>12.3</v>
       </c>
       <c r="D12" t="n">
-        <v>201150</v>
+        <v>246000</v>
       </c>
       <c r="E12" t="n">
-        <v>4.88</v>
+        <v>10.9</v>
       </c>
       <c r="F12" t="n">
-        <v>131760</v>
+        <v>218000</v>
       </c>
       <c r="G12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H12" t="n">
-        <v>4.16</v>
+        <v>5.51</v>
       </c>
       <c r="I12" t="n">
-        <v>6.35</v>
+        <v>6.21</v>
       </c>
       <c r="J12" t="n">
         <v>11</v>
       </c>
       <c r="K12" t="n">
-        <v>8370</v>
+        <v>13548</v>
       </c>
     </row>
   </sheetData>

--- a/Excel025-div-rank.xlsx
+++ b/Excel025-div-rank.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,34 +492,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80000</v>
+        <v>75000</v>
       </c>
       <c r="C2" t="n">
-        <v>14.85</v>
+        <v>15.3</v>
       </c>
       <c r="D2" t="n">
-        <v>1188000</v>
+        <v>1147500</v>
       </c>
       <c r="E2" t="n">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="F2" t="n">
-        <v>648000</v>
+        <v>577500</v>
       </c>
       <c r="G2" t="n">
         <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>6.4</v>
+        <v>6.21</v>
       </c>
       <c r="I2" t="n">
-        <v>11.73</v>
+        <v>12.34</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>76000</v>
+        <v>71250</v>
       </c>
     </row>
     <row r="3">
@@ -538,25 +538,25 @@
         <v>534750</v>
       </c>
       <c r="E3" t="n">
-        <v>6.75</v>
+        <v>7.6</v>
       </c>
       <c r="F3" t="n">
-        <v>465750</v>
+        <v>524400</v>
       </c>
       <c r="G3" t="n">
         <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>10.04</v>
+        <v>9.91</v>
       </c>
       <c r="I3" t="n">
-        <v>11.53</v>
+        <v>10.1</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>53695.8</v>
+        <v>52978.2</v>
       </c>
     </row>
     <row r="4">
@@ -599,38 +599,38 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WHAIR</t>
+          <t>SENA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50000</v>
+        <v>105000</v>
       </c>
       <c r="C5" t="n">
-        <v>8.699999999999999</v>
+        <v>4.48</v>
       </c>
       <c r="D5" t="n">
-        <v>435000</v>
+        <v>470400</v>
       </c>
       <c r="E5" t="n">
-        <v>7.6</v>
+        <v>1.72</v>
       </c>
       <c r="F5" t="n">
-        <v>380000</v>
+        <v>180600</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H5" t="n">
-        <v>6.59</v>
+        <v>3.09</v>
       </c>
       <c r="I5" t="n">
-        <v>7.54</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="J5" t="n">
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>28650</v>
+        <v>14521.5</v>
       </c>
     </row>
     <row r="6">
@@ -649,10 +649,10 @@
         <v>1212000</v>
       </c>
       <c r="E6" t="n">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="F6" t="n">
-        <v>828000</v>
+        <v>780000</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -661,7 +661,7 @@
         <v>5.11</v>
       </c>
       <c r="I6" t="n">
-        <v>7.48</v>
+        <v>7.94</v>
       </c>
       <c r="J6" t="n">
         <v>5</v>
@@ -673,222 +673,296 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SENA</t>
+          <t>WHAIR</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>105000</v>
+        <v>50000</v>
       </c>
       <c r="C7" t="n">
-        <v>4.48</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>470400</v>
+        <v>435000</v>
       </c>
       <c r="E7" t="n">
-        <v>1.93</v>
+        <v>7.75</v>
       </c>
       <c r="F7" t="n">
-        <v>202650</v>
+        <v>387500</v>
       </c>
       <c r="G7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>3.09</v>
+        <v>6.59</v>
       </c>
       <c r="I7" t="n">
-        <v>7.17</v>
+        <v>7.39</v>
       </c>
       <c r="J7" t="n">
         <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>14521.5</v>
+        <v>28650</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TFFIF</t>
+          <t>AIMIRT</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25000</v>
+        <v>10000</v>
       </c>
       <c r="C8" t="n">
-        <v>7.3</v>
+        <v>11.3</v>
       </c>
       <c r="D8" t="n">
-        <v>182500</v>
+        <v>113000</v>
       </c>
       <c r="E8" t="n">
-        <v>6.55</v>
+        <v>11.5</v>
       </c>
       <c r="F8" t="n">
-        <v>163750</v>
+        <v>115000</v>
       </c>
       <c r="G8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H8" t="n">
-        <v>6.39</v>
+        <v>7.26</v>
       </c>
       <c r="I8" t="n">
-        <v>7.12</v>
+        <v>7.13</v>
       </c>
       <c r="J8" t="n">
         <v>7</v>
       </c>
       <c r="K8" t="n">
-        <v>11657.5</v>
+        <v>8200</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CPNREIT</t>
+          <t>NER</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>55000</v>
+        <v>27000</v>
       </c>
       <c r="C9" t="n">
-        <v>18</v>
+        <v>7.45</v>
       </c>
       <c r="D9" t="n">
-        <v>990000</v>
+        <v>201150</v>
       </c>
       <c r="E9" t="n">
-        <v>12.2</v>
+        <v>4.36</v>
       </c>
       <c r="F9" t="n">
-        <v>671000</v>
+        <v>117720</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H9" t="n">
-        <v>4.58</v>
+        <v>4.16</v>
       </c>
       <c r="I9" t="n">
-        <v>6.76</v>
+        <v>7.11</v>
       </c>
       <c r="J9" t="n">
         <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>45380.5</v>
+        <v>8370</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NER</t>
+          <t>PROSPECT</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27000</v>
+        <v>20000</v>
       </c>
       <c r="C10" t="n">
-        <v>7.45</v>
+        <v>9.4</v>
       </c>
       <c r="D10" t="n">
-        <v>201150</v>
+        <v>188000</v>
       </c>
       <c r="E10" t="n">
-        <v>4.68</v>
+        <v>10.2</v>
       </c>
       <c r="F10" t="n">
-        <v>126360</v>
+        <v>204000</v>
       </c>
       <c r="G10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>4.16</v>
+        <v>7.68</v>
       </c>
       <c r="I10" t="n">
-        <v>6.62</v>
+        <v>7.07</v>
       </c>
       <c r="J10" t="n">
         <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>8370</v>
+        <v>14430</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PTT</t>
+          <t>TFFIF</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7500</v>
+        <v>25000</v>
       </c>
       <c r="C11" t="n">
-        <v>32</v>
+        <v>7.3</v>
       </c>
       <c r="D11" t="n">
-        <v>240000</v>
+        <v>182500</v>
       </c>
       <c r="E11" t="n">
-        <v>35.25</v>
+        <v>6.7</v>
       </c>
       <c r="F11" t="n">
-        <v>264375</v>
+        <v>167500</v>
       </c>
       <c r="G11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H11" t="n">
-        <v>7.19</v>
+        <v>6.37</v>
       </c>
       <c r="I11" t="n">
-        <v>6.52</v>
+        <v>6.94</v>
       </c>
       <c r="J11" t="n">
         <v>10</v>
       </c>
       <c r="K11" t="n">
-        <v>17250</v>
+        <v>11620</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WHART</t>
+          <t>CPNREIT</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20000</v>
+        <v>55000</v>
       </c>
       <c r="C12" t="n">
-        <v>12.3</v>
+        <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>246000</v>
+        <v>990000</v>
       </c>
       <c r="E12" t="n">
-        <v>10.9</v>
+        <v>12.9</v>
       </c>
       <c r="F12" t="n">
-        <v>218000</v>
+        <v>709500</v>
       </c>
       <c r="G12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>5.51</v>
+        <v>4.75</v>
       </c>
       <c r="I12" t="n">
-        <v>6.21</v>
+        <v>6.62</v>
       </c>
       <c r="J12" t="n">
         <v>11</v>
       </c>
       <c r="K12" t="n">
+        <v>47003</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PTT</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>7500</v>
+      </c>
+      <c r="C13" t="n">
+        <v>32</v>
+      </c>
+      <c r="D13" t="n">
+        <v>240000</v>
+      </c>
+      <c r="E13" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>266250</v>
+      </c>
+      <c r="G13" t="n">
+        <v>7</v>
+      </c>
+      <c r="H13" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="I13" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="J13" t="n">
+        <v>12</v>
+      </c>
+      <c r="K13" t="n">
+        <v>17250</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>WHART</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C14" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>246000</v>
+      </c>
+      <c r="E14" t="n">
+        <v>11</v>
+      </c>
+      <c r="F14" t="n">
+        <v>220000</v>
+      </c>
+      <c r="G14" t="n">
+        <v>8</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="I14" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="J14" t="n">
+        <v>13</v>
+      </c>
+      <c r="K14" t="n">
         <v>13548</v>
       </c>
     </row>

--- a/Excel025-div-rank.xlsx
+++ b/Excel025-div-rank.xlsx
@@ -501,10 +501,10 @@
         <v>1147500</v>
       </c>
       <c r="E2" t="n">
-        <v>7.7</v>
+        <v>7.95</v>
       </c>
       <c r="F2" t="n">
-        <v>577500</v>
+        <v>596250</v>
       </c>
       <c r="G2" t="n">
         <v>3</v>
@@ -513,7 +513,7 @@
         <v>6.21</v>
       </c>
       <c r="I2" t="n">
-        <v>12.34</v>
+        <v>11.95</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -538,10 +538,10 @@
         <v>534750</v>
       </c>
       <c r="E3" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>524400</v>
+        <v>565800</v>
       </c>
       <c r="G3" t="n">
         <v>4</v>
@@ -550,7 +550,7 @@
         <v>9.91</v>
       </c>
       <c r="I3" t="n">
-        <v>10.1</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
@@ -575,10 +575,10 @@
         <v>571500</v>
       </c>
       <c r="E4" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="F4" t="n">
-        <v>454500</v>
+        <v>459000</v>
       </c>
       <c r="G4" t="n">
         <v>5</v>
@@ -587,7 +587,7 @@
         <v>7</v>
       </c>
       <c r="I4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
@@ -599,75 +599,75 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SENA</t>
+          <t>3BBIF</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>105000</v>
+        <v>120000</v>
       </c>
       <c r="C5" t="n">
-        <v>4.48</v>
+        <v>10.1</v>
       </c>
       <c r="D5" t="n">
-        <v>470400</v>
+        <v>1212000</v>
       </c>
       <c r="E5" t="n">
-        <v>1.72</v>
+        <v>6.55</v>
       </c>
       <c r="F5" t="n">
-        <v>180600</v>
+        <v>786000</v>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>3.09</v>
+        <v>5.11</v>
       </c>
       <c r="I5" t="n">
-        <v>8.039999999999999</v>
+        <v>7.88</v>
       </c>
       <c r="J5" t="n">
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>14521.5</v>
+        <v>61908</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3BBIF</t>
+          <t>SENA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>120000</v>
+        <v>105000</v>
       </c>
       <c r="C6" t="n">
-        <v>10.1</v>
+        <v>4.48</v>
       </c>
       <c r="D6" t="n">
-        <v>1212000</v>
+        <v>470400</v>
       </c>
       <c r="E6" t="n">
-        <v>6.5</v>
+        <v>1.81</v>
       </c>
       <c r="F6" t="n">
-        <v>780000</v>
+        <v>190050</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H6" t="n">
-        <v>5.11</v>
+        <v>3.09</v>
       </c>
       <c r="I6" t="n">
-        <v>7.94</v>
+        <v>7.64</v>
       </c>
       <c r="J6" t="n">
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>61908</v>
+        <v>14521.5</v>
       </c>
     </row>
     <row r="7">
@@ -686,10 +686,10 @@
         <v>435000</v>
       </c>
       <c r="E7" t="n">
-        <v>7.75</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>387500</v>
+        <v>410000</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
@@ -698,7 +698,7 @@
         <v>6.59</v>
       </c>
       <c r="I7" t="n">
-        <v>7.39</v>
+        <v>6.99</v>
       </c>
       <c r="J7" t="n">
         <v>6</v>
@@ -710,38 +710,38 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AIMIRT</t>
+          <t>PROSPECT</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="C8" t="n">
-        <v>11.3</v>
+        <v>9.4</v>
       </c>
       <c r="D8" t="n">
-        <v>113000</v>
+        <v>188000</v>
       </c>
       <c r="E8" t="n">
-        <v>11.5</v>
+        <v>10.4</v>
       </c>
       <c r="F8" t="n">
-        <v>115000</v>
+        <v>208000</v>
       </c>
       <c r="G8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H8" t="n">
-        <v>7.26</v>
+        <v>7.68</v>
       </c>
       <c r="I8" t="n">
-        <v>7.13</v>
+        <v>6.94</v>
       </c>
       <c r="J8" t="n">
         <v>7</v>
       </c>
       <c r="K8" t="n">
-        <v>8200</v>
+        <v>14430</v>
       </c>
     </row>
     <row r="9">
@@ -760,19 +760,19 @@
         <v>201150</v>
       </c>
       <c r="E9" t="n">
-        <v>4.36</v>
+        <v>4.5</v>
       </c>
       <c r="F9" t="n">
-        <v>117720</v>
+        <v>121500</v>
       </c>
       <c r="G9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H9" t="n">
         <v>4.16</v>
       </c>
       <c r="I9" t="n">
-        <v>7.11</v>
+        <v>6.89</v>
       </c>
       <c r="J9" t="n">
         <v>8</v>
@@ -784,75 +784,75 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PROSPECT</t>
+          <t>TFFIF</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="C10" t="n">
-        <v>9.4</v>
+        <v>7.3</v>
       </c>
       <c r="D10" t="n">
-        <v>188000</v>
+        <v>182500</v>
       </c>
       <c r="E10" t="n">
-        <v>10.2</v>
+        <v>6.9</v>
       </c>
       <c r="F10" t="n">
-        <v>204000</v>
+        <v>172500</v>
       </c>
       <c r="G10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H10" t="n">
-        <v>7.68</v>
+        <v>6.37</v>
       </c>
       <c r="I10" t="n">
-        <v>7.07</v>
+        <v>6.74</v>
       </c>
       <c r="J10" t="n">
         <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>14430</v>
+        <v>11620</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TFFIF</t>
+          <t>AIMIRT</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25000</v>
+        <v>10000</v>
       </c>
       <c r="C11" t="n">
-        <v>7.3</v>
+        <v>11.3</v>
       </c>
       <c r="D11" t="n">
-        <v>182500</v>
+        <v>113000</v>
       </c>
       <c r="E11" t="n">
-        <v>6.7</v>
+        <v>12.3</v>
       </c>
       <c r="F11" t="n">
-        <v>167500</v>
+        <v>123000</v>
       </c>
       <c r="G11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H11" t="n">
-        <v>6.37</v>
+        <v>7.26</v>
       </c>
       <c r="I11" t="n">
-        <v>6.94</v>
+        <v>6.67</v>
       </c>
       <c r="J11" t="n">
         <v>10</v>
       </c>
       <c r="K11" t="n">
-        <v>11620</v>
+        <v>8200</v>
       </c>
     </row>
     <row r="12">
@@ -871,10 +871,10 @@
         <v>990000</v>
       </c>
       <c r="E12" t="n">
-        <v>12.9</v>
+        <v>13.4</v>
       </c>
       <c r="F12" t="n">
-        <v>709500</v>
+        <v>737000</v>
       </c>
       <c r="G12" t="n">
         <v>2</v>
@@ -883,7 +883,7 @@
         <v>4.75</v>
       </c>
       <c r="I12" t="n">
-        <v>6.62</v>
+        <v>6.38</v>
       </c>
       <c r="J12" t="n">
         <v>11</v>
@@ -908,10 +908,10 @@
         <v>240000</v>
       </c>
       <c r="E13" t="n">
-        <v>35.5</v>
+        <v>38.5</v>
       </c>
       <c r="F13" t="n">
-        <v>266250</v>
+        <v>288750</v>
       </c>
       <c r="G13" t="n">
         <v>7</v>
@@ -920,7 +920,7 @@
         <v>7.19</v>
       </c>
       <c r="I13" t="n">
-        <v>6.48</v>
+        <v>5.97</v>
       </c>
       <c r="J13" t="n">
         <v>12</v>
@@ -945,10 +945,10 @@
         <v>246000</v>
       </c>
       <c r="E14" t="n">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="F14" t="n">
-        <v>220000</v>
+        <v>228000</v>
       </c>
       <c r="G14" t="n">
         <v>8</v>
@@ -957,7 +957,7 @@
         <v>5.51</v>
       </c>
       <c r="I14" t="n">
-        <v>6.16</v>
+        <v>5.94</v>
       </c>
       <c r="J14" t="n">
         <v>13</v>
